--- a/activity/M01A11/M01A11_BordeLibre.xlsx
+++ b/activity/M01A11/M01A11_BordeLibre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0B02D8-8D1C-4DC8-8D3B-91BC0FE8A392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13966316-405F-4CAA-AA64-59C76D824E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -534,7 +534,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -610,47 +610,17 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -681,11 +651,35 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -791,11 +785,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calificacion!$D$4</c:f>
+              <c:f>Calificacion!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Calificación Instructor</c:v>
+                  <c:v>Calificación final</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -807,12 +801,7 @@
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -826,13 +815,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -844,7 +833,6 @@
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inBase"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -854,7 +842,21 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -883,7 +885,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calificacion!$D$5:$D$9</c:f>
+              <c:f>Calificacion!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2096,7 +2098,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="26" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2137,14 +2139,14 @@
       <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="27">
         <v>5</v>
       </c>
       <c r="D5" s="21">
         <f>Detalle!C44*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="27"/>
       <c r="F5" s="23">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2154,14 +2156,14 @@
       <c r="B6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="27">
         <v>5</v>
       </c>
       <c r="D6" s="21">
         <f>Detalle!F44*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="35"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="23">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2171,14 +2173,14 @@
       <c r="B7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="27">
         <v>5</v>
       </c>
       <c r="D7" s="21">
         <f>Detalle!I44*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="35"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2188,14 +2190,14 @@
       <c r="B8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="27">
         <v>5</v>
       </c>
       <c r="D8" s="21">
         <f>Detalle!L44*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="35"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2205,14 +2207,14 @@
       <c r="B9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="27">
         <v>5</v>
       </c>
       <c r="D9" s="21">
         <f>Detalle!O44*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="35"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2222,14 +2224,14 @@
       <c r="B10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="27">
         <v>5</v>
       </c>
       <c r="D10" s="21">
         <f>Detalle!R44*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="35"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2239,14 +2241,14 @@
       <c r="B11" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="27">
         <v>5</v>
       </c>
       <c r="D11" s="21">
         <f>Detalle!U44*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="35"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2256,14 +2258,14 @@
       <c r="B12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="27">
         <v>5</v>
       </c>
       <c r="D12" s="21">
         <f>Detalle!X44*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="27"/>
       <c r="F12" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2273,14 +2275,14 @@
       <c r="B13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="27">
         <v>5</v>
       </c>
       <c r="D13" s="21">
         <f>Detalle!AA44*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2290,14 +2292,14 @@
       <c r="B14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="27">
         <v>5</v>
       </c>
       <c r="D14" s="21">
         <f>Detalle!AD44*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="35"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2307,14 +2309,14 @@
       <c r="B15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="27">
         <v>5</v>
       </c>
       <c r="D15" s="21">
         <f>Detalle!AG44*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2324,14 +2326,14 @@
       <c r="B16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="27">
         <v>5</v>
       </c>
       <c r="D16" s="21">
         <f>Detalle!AJ44*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="35"/>
+      <c r="E16" s="27"/>
       <c r="F16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2341,14 +2343,14 @@
       <c r="B17" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="27">
         <v>5</v>
       </c>
       <c r="D17" s="21">
         <f>Detalle!AM44*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2358,42 +2360,42 @@
       <c r="B18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="28">
         <v>5</v>
       </c>
       <c r="D18" s="22">
         <f>Detalle!AP44*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="36"/>
+      <c r="E18" s="28"/>
       <c r="F18" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="31" t="str">
+      <c r="B19" s="39" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A11 en GitHub.</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2499,96 +2501,96 @@
     </row>
     <row r="2" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="25" t="str">
+      <c r="C2" s="40" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="25" t="str">
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="40" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="25" t="str">
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="40" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="25" t="str">
+      <c r="J2" s="41"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="40" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="26"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="25" t="str">
+      <c r="M2" s="41"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="40" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="25" t="str">
+      <c r="P2" s="41"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="40" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="26"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="25" t="str">
+      <c r="S2" s="41"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="40" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="26"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="25" t="str">
+      <c r="V2" s="41"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="40" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="25" t="str">
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="40" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="25" t="str">
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="40" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="25" t="str">
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="40" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="27"/>
-      <c r="AJ2" s="25" t="str">
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="40" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="26"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="25" t="str">
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="42"/>
+      <c r="AM2" s="40" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="26"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="25" t="str">
+      <c r="AN2" s="41"/>
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="40" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="26"/>
-      <c r="AR2" s="27"/>
+      <c r="AQ2" s="41"/>
+      <c r="AR2" s="42"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="29"/>
+      <c r="B3" s="46"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2720,1997 +2722,1997 @@
       <c r="B4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="39"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="39"/>
-      <c r="AB4" s="40"/>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="40"/>
-      <c r="AF4" s="41"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="40"/>
-      <c r="AI4" s="41"/>
-      <c r="AJ4" s="39"/>
-      <c r="AK4" s="40"/>
-      <c r="AL4" s="41"/>
-      <c r="AM4" s="39"/>
-      <c r="AN4" s="40"/>
-      <c r="AO4" s="41"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="40"/>
-      <c r="AR4" s="41"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="31"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="31"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="31"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="39">
-        <v>0</v>
-      </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="39">
-        <v>0</v>
-      </c>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="39">
-        <v>0</v>
-      </c>
-      <c r="J5" s="40"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="39">
-        <v>0</v>
-      </c>
-      <c r="M5" s="40"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="39">
-        <v>0</v>
-      </c>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="39">
-        <v>0</v>
-      </c>
-      <c r="S5" s="40"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="39">
-        <v>0</v>
-      </c>
-      <c r="V5" s="40"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="39">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="40"/>
-      <c r="AC5" s="41"/>
-      <c r="AD5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="40"/>
-      <c r="AL5" s="41"/>
-      <c r="AM5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="40"/>
-      <c r="AO5" s="41"/>
-      <c r="AP5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="40"/>
-      <c r="AR5" s="41"/>
+      <c r="C5" s="29">
+        <v>0</v>
+      </c>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="29">
+        <v>0</v>
+      </c>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="29">
+        <v>0</v>
+      </c>
+      <c r="J5" s="30"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="29">
+        <v>0</v>
+      </c>
+      <c r="M5" s="30"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="29">
+        <v>0</v>
+      </c>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="29">
+        <v>0</v>
+      </c>
+      <c r="S5" s="30"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="29">
+        <v>0</v>
+      </c>
+      <c r="V5" s="30"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="31"/>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="39"/>
-      <c r="AB6" s="40"/>
-      <c r="AC6" s="41"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="41"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="40"/>
-      <c r="AL6" s="41"/>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="40"/>
-      <c r="AO6" s="41"/>
-      <c r="AP6" s="39"/>
-      <c r="AQ6" s="40"/>
-      <c r="AR6" s="41"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="31"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="31"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="39"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="40"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="40"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="39"/>
-      <c r="AK7" s="40"/>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="41"/>
-      <c r="AP7" s="39"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="41"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="31"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="31"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="40"/>
-      <c r="AC8" s="41"/>
-      <c r="AD8" s="39"/>
-      <c r="AE8" s="40"/>
-      <c r="AF8" s="41"/>
-      <c r="AG8" s="39"/>
-      <c r="AH8" s="40"/>
-      <c r="AI8" s="41"/>
-      <c r="AJ8" s="39"/>
-      <c r="AK8" s="40"/>
-      <c r="AL8" s="41"/>
-      <c r="AM8" s="39"/>
-      <c r="AN8" s="40"/>
-      <c r="AO8" s="41"/>
-      <c r="AP8" s="39"/>
-      <c r="AQ8" s="40"/>
-      <c r="AR8" s="41"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="30"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="30"/>
+      <c r="AR8" s="31"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="39"/>
-      <c r="AH9" s="40"/>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="39"/>
-      <c r="AK9" s="40"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="39"/>
-      <c r="AN9" s="40"/>
-      <c r="AO9" s="41"/>
-      <c r="AP9" s="39"/>
-      <c r="AQ9" s="40"/>
-      <c r="AR9" s="41"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="31"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="40"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="39"/>
-      <c r="AB10" s="40"/>
-      <c r="AC10" s="41"/>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="40"/>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="40"/>
-      <c r="AI10" s="41"/>
-      <c r="AJ10" s="39"/>
-      <c r="AK10" s="40"/>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="39"/>
-      <c r="AN10" s="40"/>
-      <c r="AO10" s="41"/>
-      <c r="AP10" s="39"/>
-      <c r="AQ10" s="40"/>
-      <c r="AR10" s="41"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="30"/>
+      <c r="AR10" s="31"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="41"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="41"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="41"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="41"/>
-      <c r="AJ11" s="39"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="41"/>
-      <c r="AM11" s="39"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="41"/>
-      <c r="AP11" s="39"/>
-      <c r="AQ11" s="40"/>
-      <c r="AR11" s="41"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="31"/>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="40"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="40"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="40"/>
-      <c r="AF12" s="41"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="40"/>
-      <c r="AI12" s="41"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="40"/>
-      <c r="AL12" s="41"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="40"/>
-      <c r="AO12" s="41"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="40"/>
-      <c r="AR12" s="41"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="30"/>
+      <c r="AR12" s="31"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="39"/>
-      <c r="V13" s="40"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="40"/>
-      <c r="Z13" s="41"/>
-      <c r="AA13" s="39"/>
-      <c r="AB13" s="40"/>
-      <c r="AC13" s="41"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="40"/>
-      <c r="AF13" s="41"/>
-      <c r="AG13" s="39"/>
-      <c r="AH13" s="40"/>
-      <c r="AI13" s="41"/>
-      <c r="AJ13" s="39"/>
-      <c r="AK13" s="40"/>
-      <c r="AL13" s="41"/>
-      <c r="AM13" s="39"/>
-      <c r="AN13" s="40"/>
-      <c r="AO13" s="41"/>
-      <c r="AP13" s="39"/>
-      <c r="AQ13" s="40"/>
-      <c r="AR13" s="41"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="30"/>
+      <c r="AO13" s="31"/>
+      <c r="AP13" s="29"/>
+      <c r="AQ13" s="30"/>
+      <c r="AR13" s="31"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="40"/>
-      <c r="Z14" s="41"/>
-      <c r="AA14" s="39"/>
-      <c r="AB14" s="40"/>
-      <c r="AC14" s="41"/>
-      <c r="AD14" s="39"/>
-      <c r="AE14" s="40"/>
-      <c r="AF14" s="41"/>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="40"/>
-      <c r="AI14" s="41"/>
-      <c r="AJ14" s="39"/>
-      <c r="AK14" s="40"/>
-      <c r="AL14" s="41"/>
-      <c r="AM14" s="39"/>
-      <c r="AN14" s="40"/>
-      <c r="AO14" s="41"/>
-      <c r="AP14" s="39"/>
-      <c r="AQ14" s="40"/>
-      <c r="AR14" s="41"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="31"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="31"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="30"/>
+      <c r="AO14" s="31"/>
+      <c r="AP14" s="29"/>
+      <c r="AQ14" s="30"/>
+      <c r="AR14" s="31"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="40"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="39"/>
-      <c r="AB15" s="40"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="41"/>
-      <c r="AM15" s="39"/>
-      <c r="AN15" s="40"/>
-      <c r="AO15" s="41"/>
-      <c r="AP15" s="39"/>
-      <c r="AQ15" s="40"/>
-      <c r="AR15" s="41"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="31"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="31"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="31"/>
+      <c r="AM15" s="29"/>
+      <c r="AN15" s="30"/>
+      <c r="AO15" s="31"/>
+      <c r="AP15" s="29"/>
+      <c r="AQ15" s="30"/>
+      <c r="AR15" s="31"/>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="39"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="39"/>
-      <c r="V16" s="40"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="39"/>
-      <c r="Y16" s="40"/>
-      <c r="Z16" s="41"/>
-      <c r="AA16" s="39"/>
-      <c r="AB16" s="40"/>
-      <c r="AC16" s="41"/>
-      <c r="AD16" s="39"/>
-      <c r="AE16" s="40"/>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="39"/>
-      <c r="AH16" s="40"/>
-      <c r="AI16" s="41"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="40"/>
-      <c r="AL16" s="41"/>
-      <c r="AM16" s="39"/>
-      <c r="AN16" s="40"/>
-      <c r="AO16" s="41"/>
-      <c r="AP16" s="39"/>
-      <c r="AQ16" s="40"/>
-      <c r="AR16" s="41"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="30"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="31"/>
+      <c r="AG16" s="29"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="31"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="31"/>
+      <c r="AM16" s="29"/>
+      <c r="AN16" s="30"/>
+      <c r="AO16" s="31"/>
+      <c r="AP16" s="29"/>
+      <c r="AQ16" s="30"/>
+      <c r="AR16" s="31"/>
     </row>
     <row r="17" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="39"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="39"/>
-      <c r="V17" s="40"/>
-      <c r="W17" s="41"/>
-      <c r="X17" s="39"/>
-      <c r="Y17" s="40"/>
-      <c r="Z17" s="41"/>
-      <c r="AA17" s="39"/>
-      <c r="AB17" s="40"/>
-      <c r="AC17" s="41"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="40"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="39"/>
-      <c r="AH17" s="40"/>
-      <c r="AI17" s="41"/>
-      <c r="AJ17" s="39"/>
-      <c r="AK17" s="40"/>
-      <c r="AL17" s="41"/>
-      <c r="AM17" s="39"/>
-      <c r="AN17" s="40"/>
-      <c r="AO17" s="41"/>
-      <c r="AP17" s="39"/>
-      <c r="AQ17" s="40"/>
-      <c r="AR17" s="41"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="29"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="31"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="31"/>
+      <c r="AM17" s="29"/>
+      <c r="AN17" s="30"/>
+      <c r="AO17" s="31"/>
+      <c r="AP17" s="29"/>
+      <c r="AQ17" s="30"/>
+      <c r="AR17" s="31"/>
     </row>
     <row r="18" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B18" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="40"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="39"/>
-      <c r="V18" s="40"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="39"/>
-      <c r="Y18" s="40"/>
-      <c r="Z18" s="41"/>
-      <c r="AA18" s="39"/>
-      <c r="AB18" s="40"/>
-      <c r="AC18" s="41"/>
-      <c r="AD18" s="39"/>
-      <c r="AE18" s="40"/>
-      <c r="AF18" s="41"/>
-      <c r="AG18" s="39"/>
-      <c r="AH18" s="40"/>
-      <c r="AI18" s="41"/>
-      <c r="AJ18" s="39"/>
-      <c r="AK18" s="40"/>
-      <c r="AL18" s="41"/>
-      <c r="AM18" s="39"/>
-      <c r="AN18" s="40"/>
-      <c r="AO18" s="41"/>
-      <c r="AP18" s="39"/>
-      <c r="AQ18" s="40"/>
-      <c r="AR18" s="41"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="29"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="31"/>
+      <c r="AM18" s="29"/>
+      <c r="AN18" s="30"/>
+      <c r="AO18" s="31"/>
+      <c r="AP18" s="29"/>
+      <c r="AQ18" s="30"/>
+      <c r="AR18" s="31"/>
     </row>
     <row r="19" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B19" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="39"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="39"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="39"/>
-      <c r="V19" s="40"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="39"/>
-      <c r="Y19" s="40"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="39"/>
-      <c r="AB19" s="40"/>
-      <c r="AC19" s="41"/>
-      <c r="AD19" s="39"/>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="41"/>
-      <c r="AG19" s="39"/>
-      <c r="AH19" s="40"/>
-      <c r="AI19" s="41"/>
-      <c r="AJ19" s="39"/>
-      <c r="AK19" s="40"/>
-      <c r="AL19" s="41"/>
-      <c r="AM19" s="39"/>
-      <c r="AN19" s="40"/>
-      <c r="AO19" s="41"/>
-      <c r="AP19" s="39"/>
-      <c r="AQ19" s="40"/>
-      <c r="AR19" s="41"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="30"/>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="29"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="29"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="31"/>
+      <c r="AM19" s="29"/>
+      <c r="AN19" s="30"/>
+      <c r="AO19" s="31"/>
+      <c r="AP19" s="29"/>
+      <c r="AQ19" s="30"/>
+      <c r="AR19" s="31"/>
     </row>
     <row r="20" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B20" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="40"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="40"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="40"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="39"/>
-      <c r="AB20" s="40"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="39"/>
-      <c r="AE20" s="40"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="40"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="39"/>
-      <c r="AK20" s="40"/>
-      <c r="AL20" s="41"/>
-      <c r="AM20" s="39"/>
-      <c r="AN20" s="40"/>
-      <c r="AO20" s="41"/>
-      <c r="AP20" s="39"/>
-      <c r="AQ20" s="40"/>
-      <c r="AR20" s="41"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="29"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="31"/>
+      <c r="AJ20" s="29"/>
+      <c r="AK20" s="30"/>
+      <c r="AL20" s="31"/>
+      <c r="AM20" s="29"/>
+      <c r="AN20" s="30"/>
+      <c r="AO20" s="31"/>
+      <c r="AP20" s="29"/>
+      <c r="AQ20" s="30"/>
+      <c r="AR20" s="31"/>
     </row>
     <row r="21" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="39"/>
-      <c r="V21" s="40"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="39"/>
-      <c r="Y21" s="40"/>
-      <c r="Z21" s="41"/>
-      <c r="AA21" s="39"/>
-      <c r="AB21" s="40"/>
-      <c r="AC21" s="41"/>
-      <c r="AD21" s="39"/>
-      <c r="AE21" s="40"/>
-      <c r="AF21" s="41"/>
-      <c r="AG21" s="39"/>
-      <c r="AH21" s="40"/>
-      <c r="AI21" s="41"/>
-      <c r="AJ21" s="39"/>
-      <c r="AK21" s="40"/>
-      <c r="AL21" s="41"/>
-      <c r="AM21" s="39"/>
-      <c r="AN21" s="40"/>
-      <c r="AO21" s="41"/>
-      <c r="AP21" s="39"/>
-      <c r="AQ21" s="40"/>
-      <c r="AR21" s="41"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="30"/>
+      <c r="AC21" s="31"/>
+      <c r="AD21" s="29"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="29"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="31"/>
+      <c r="AJ21" s="29"/>
+      <c r="AK21" s="30"/>
+      <c r="AL21" s="31"/>
+      <c r="AM21" s="29"/>
+      <c r="AN21" s="30"/>
+      <c r="AO21" s="31"/>
+      <c r="AP21" s="29"/>
+      <c r="AQ21" s="30"/>
+      <c r="AR21" s="31"/>
     </row>
     <row r="22" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B22" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="39"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="39"/>
-      <c r="V22" s="40"/>
-      <c r="W22" s="41"/>
-      <c r="X22" s="39"/>
-      <c r="Y22" s="40"/>
-      <c r="Z22" s="41"/>
-      <c r="AA22" s="39"/>
-      <c r="AB22" s="40"/>
-      <c r="AC22" s="41"/>
-      <c r="AD22" s="39"/>
-      <c r="AE22" s="40"/>
-      <c r="AF22" s="41"/>
-      <c r="AG22" s="39"/>
-      <c r="AH22" s="40"/>
-      <c r="AI22" s="41"/>
-      <c r="AJ22" s="39"/>
-      <c r="AK22" s="40"/>
-      <c r="AL22" s="41"/>
-      <c r="AM22" s="39"/>
-      <c r="AN22" s="40"/>
-      <c r="AO22" s="41"/>
-      <c r="AP22" s="39"/>
-      <c r="AQ22" s="40"/>
-      <c r="AR22" s="41"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="30"/>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="29"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="29"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="29"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="31"/>
+      <c r="AM22" s="29"/>
+      <c r="AN22" s="30"/>
+      <c r="AO22" s="31"/>
+      <c r="AP22" s="29"/>
+      <c r="AQ22" s="30"/>
+      <c r="AR22" s="31"/>
     </row>
     <row r="23" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="39"/>
-      <c r="V23" s="40"/>
-      <c r="W23" s="41"/>
-      <c r="X23" s="39"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="41"/>
-      <c r="AA23" s="39"/>
-      <c r="AB23" s="40"/>
-      <c r="AC23" s="41"/>
-      <c r="AD23" s="39"/>
-      <c r="AE23" s="40"/>
-      <c r="AF23" s="41"/>
-      <c r="AG23" s="39"/>
-      <c r="AH23" s="40"/>
-      <c r="AI23" s="41"/>
-      <c r="AJ23" s="39"/>
-      <c r="AK23" s="40"/>
-      <c r="AL23" s="41"/>
-      <c r="AM23" s="39"/>
-      <c r="AN23" s="40"/>
-      <c r="AO23" s="41"/>
-      <c r="AP23" s="39"/>
-      <c r="AQ23" s="40"/>
-      <c r="AR23" s="41"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="29"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="31"/>
+      <c r="AJ23" s="29"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="31"/>
+      <c r="AM23" s="29"/>
+      <c r="AN23" s="30"/>
+      <c r="AO23" s="31"/>
+      <c r="AP23" s="29"/>
+      <c r="AQ23" s="30"/>
+      <c r="AR23" s="31"/>
     </row>
     <row r="24" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B24" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="40"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="39"/>
-      <c r="Y24" s="40"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="39"/>
-      <c r="AB24" s="40"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="39"/>
-      <c r="AE24" s="40"/>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="39"/>
-      <c r="AH24" s="40"/>
-      <c r="AI24" s="41"/>
-      <c r="AJ24" s="39"/>
-      <c r="AK24" s="40"/>
-      <c r="AL24" s="41"/>
-      <c r="AM24" s="39"/>
-      <c r="AN24" s="40"/>
-      <c r="AO24" s="41"/>
-      <c r="AP24" s="39"/>
-      <c r="AQ24" s="40"/>
-      <c r="AR24" s="41"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="29"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="29"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="31"/>
+      <c r="AJ24" s="29"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="31"/>
+      <c r="AM24" s="29"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="31"/>
+      <c r="AP24" s="29"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="31"/>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B25" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="39"/>
-      <c r="V25" s="40"/>
-      <c r="W25" s="41"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="41"/>
-      <c r="AA25" s="39"/>
-      <c r="AB25" s="40"/>
-      <c r="AC25" s="41"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="40"/>
-      <c r="AF25" s="41"/>
-      <c r="AG25" s="39"/>
-      <c r="AH25" s="40"/>
-      <c r="AI25" s="41"/>
-      <c r="AJ25" s="39"/>
-      <c r="AK25" s="40"/>
-      <c r="AL25" s="41"/>
-      <c r="AM25" s="39"/>
-      <c r="AN25" s="40"/>
-      <c r="AO25" s="41"/>
-      <c r="AP25" s="39"/>
-      <c r="AQ25" s="40"/>
-      <c r="AR25" s="41"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="29"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="31"/>
+      <c r="AJ25" s="29"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="31"/>
+      <c r="AM25" s="29"/>
+      <c r="AN25" s="30"/>
+      <c r="AO25" s="31"/>
+      <c r="AP25" s="29"/>
+      <c r="AQ25" s="30"/>
+      <c r="AR25" s="31"/>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B26" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="39"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="39"/>
-      <c r="V26" s="40"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="39"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="41"/>
-      <c r="AA26" s="39"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="41"/>
-      <c r="AD26" s="39"/>
-      <c r="AE26" s="40"/>
-      <c r="AF26" s="41"/>
-      <c r="AG26" s="39"/>
-      <c r="AH26" s="40"/>
-      <c r="AI26" s="41"/>
-      <c r="AJ26" s="39"/>
-      <c r="AK26" s="40"/>
-      <c r="AL26" s="41"/>
-      <c r="AM26" s="39"/>
-      <c r="AN26" s="40"/>
-      <c r="AO26" s="41"/>
-      <c r="AP26" s="39"/>
-      <c r="AQ26" s="40"/>
-      <c r="AR26" s="41"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="29"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="29"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="29"/>
+      <c r="AN26" s="30"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="29"/>
+      <c r="AQ26" s="30"/>
+      <c r="AR26" s="31"/>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B27" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="39"/>
-      <c r="V27" s="40"/>
-      <c r="W27" s="41"/>
-      <c r="X27" s="39"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="41"/>
-      <c r="AA27" s="39"/>
-      <c r="AB27" s="40"/>
-      <c r="AC27" s="41"/>
-      <c r="AD27" s="39"/>
-      <c r="AE27" s="40"/>
-      <c r="AF27" s="41"/>
-      <c r="AG27" s="39"/>
-      <c r="AH27" s="40"/>
-      <c r="AI27" s="41"/>
-      <c r="AJ27" s="39"/>
-      <c r="AK27" s="40"/>
-      <c r="AL27" s="41"/>
-      <c r="AM27" s="39"/>
-      <c r="AN27" s="40"/>
-      <c r="AO27" s="41"/>
-      <c r="AP27" s="39"/>
-      <c r="AQ27" s="40"/>
-      <c r="AR27" s="41"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="29"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="31"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="31"/>
+      <c r="AM27" s="29"/>
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="31"/>
+      <c r="AP27" s="29"/>
+      <c r="AQ27" s="30"/>
+      <c r="AR27" s="31"/>
     </row>
     <row r="28" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B28" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="39"/>
-      <c r="V28" s="40"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="39"/>
-      <c r="Y28" s="40"/>
-      <c r="Z28" s="41"/>
-      <c r="AA28" s="39"/>
-      <c r="AB28" s="40"/>
-      <c r="AC28" s="41"/>
-      <c r="AD28" s="39"/>
-      <c r="AE28" s="40"/>
-      <c r="AF28" s="41"/>
-      <c r="AG28" s="39"/>
-      <c r="AH28" s="40"/>
-      <c r="AI28" s="41"/>
-      <c r="AJ28" s="39"/>
-      <c r="AK28" s="40"/>
-      <c r="AL28" s="41"/>
-      <c r="AM28" s="39"/>
-      <c r="AN28" s="40"/>
-      <c r="AO28" s="41"/>
-      <c r="AP28" s="39"/>
-      <c r="AQ28" s="40"/>
-      <c r="AR28" s="41"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="29"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="31"/>
+      <c r="AM28" s="29"/>
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="31"/>
+      <c r="AP28" s="29"/>
+      <c r="AQ28" s="30"/>
+      <c r="AR28" s="31"/>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="40"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="41"/>
-      <c r="AA29" s="39"/>
-      <c r="AB29" s="40"/>
-      <c r="AC29" s="41"/>
-      <c r="AD29" s="39"/>
-      <c r="AE29" s="40"/>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="39"/>
-      <c r="AH29" s="40"/>
-      <c r="AI29" s="41"/>
-      <c r="AJ29" s="39"/>
-      <c r="AK29" s="40"/>
-      <c r="AL29" s="41"/>
-      <c r="AM29" s="39"/>
-      <c r="AN29" s="40"/>
-      <c r="AO29" s="41"/>
-      <c r="AP29" s="39"/>
-      <c r="AQ29" s="40"/>
-      <c r="AR29" s="41"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="29"/>
+      <c r="AH29" s="30"/>
+      <c r="AI29" s="31"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="30"/>
+      <c r="AL29" s="31"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="30"/>
+      <c r="AO29" s="31"/>
+      <c r="AP29" s="29"/>
+      <c r="AQ29" s="30"/>
+      <c r="AR29" s="31"/>
     </row>
     <row r="30" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B30" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="40"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="40"/>
-      <c r="Z30" s="41"/>
-      <c r="AA30" s="39"/>
-      <c r="AB30" s="40"/>
-      <c r="AC30" s="41"/>
-      <c r="AD30" s="39"/>
-      <c r="AE30" s="40"/>
-      <c r="AF30" s="41"/>
-      <c r="AG30" s="39"/>
-      <c r="AH30" s="40"/>
-      <c r="AI30" s="41"/>
-      <c r="AJ30" s="39"/>
-      <c r="AK30" s="40"/>
-      <c r="AL30" s="41"/>
-      <c r="AM30" s="39"/>
-      <c r="AN30" s="40"/>
-      <c r="AO30" s="41"/>
-      <c r="AP30" s="39"/>
-      <c r="AQ30" s="40"/>
-      <c r="AR30" s="41"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="29"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="29"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="29"/>
+      <c r="AK30" s="30"/>
+      <c r="AL30" s="31"/>
+      <c r="AM30" s="29"/>
+      <c r="AN30" s="30"/>
+      <c r="AO30" s="31"/>
+      <c r="AP30" s="29"/>
+      <c r="AQ30" s="30"/>
+      <c r="AR30" s="31"/>
     </row>
     <row r="31" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B31" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="39"/>
-      <c r="V31" s="40"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="39"/>
-      <c r="Y31" s="40"/>
-      <c r="Z31" s="41"/>
-      <c r="AA31" s="39"/>
-      <c r="AB31" s="40"/>
-      <c r="AC31" s="41"/>
-      <c r="AD31" s="39"/>
-      <c r="AE31" s="40"/>
-      <c r="AF31" s="41"/>
-      <c r="AG31" s="39"/>
-      <c r="AH31" s="40"/>
-      <c r="AI31" s="41"/>
-      <c r="AJ31" s="39"/>
-      <c r="AK31" s="40"/>
-      <c r="AL31" s="41"/>
-      <c r="AM31" s="39"/>
-      <c r="AN31" s="40"/>
-      <c r="AO31" s="41"/>
-      <c r="AP31" s="39"/>
-      <c r="AQ31" s="40"/>
-      <c r="AR31" s="41"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="29"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="29"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="29"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="31"/>
+      <c r="AJ31" s="29"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="31"/>
+      <c r="AM31" s="29"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="31"/>
+      <c r="AP31" s="29"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="31"/>
     </row>
     <row r="32" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B32" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="41"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="39"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="39"/>
-      <c r="V32" s="40"/>
-      <c r="W32" s="41"/>
-      <c r="X32" s="39"/>
-      <c r="Y32" s="40"/>
-      <c r="Z32" s="41"/>
-      <c r="AA32" s="39"/>
-      <c r="AB32" s="40"/>
-      <c r="AC32" s="41"/>
-      <c r="AD32" s="39"/>
-      <c r="AE32" s="40"/>
-      <c r="AF32" s="41"/>
-      <c r="AG32" s="39"/>
-      <c r="AH32" s="40"/>
-      <c r="AI32" s="41"/>
-      <c r="AJ32" s="39"/>
-      <c r="AK32" s="40"/>
-      <c r="AL32" s="41"/>
-      <c r="AM32" s="39"/>
-      <c r="AN32" s="40"/>
-      <c r="AO32" s="41"/>
-      <c r="AP32" s="39"/>
-      <c r="AQ32" s="40"/>
-      <c r="AR32" s="41"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="29"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="31"/>
+      <c r="AG32" s="29"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="31"/>
+      <c r="AJ32" s="29"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="31"/>
+      <c r="AM32" s="29"/>
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="31"/>
+      <c r="AP32" s="29"/>
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="31"/>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B33" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="40"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="39"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="39"/>
-      <c r="V33" s="40"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="39"/>
-      <c r="Y33" s="40"/>
-      <c r="Z33" s="41"/>
-      <c r="AA33" s="39"/>
-      <c r="AB33" s="40"/>
-      <c r="AC33" s="41"/>
-      <c r="AD33" s="39"/>
-      <c r="AE33" s="40"/>
-      <c r="AF33" s="41"/>
-      <c r="AG33" s="39"/>
-      <c r="AH33" s="40"/>
-      <c r="AI33" s="41"/>
-      <c r="AJ33" s="39"/>
-      <c r="AK33" s="40"/>
-      <c r="AL33" s="41"/>
-      <c r="AM33" s="39"/>
-      <c r="AN33" s="40"/>
-      <c r="AO33" s="41"/>
-      <c r="AP33" s="39"/>
-      <c r="AQ33" s="40"/>
-      <c r="AR33" s="41"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="29"/>
+      <c r="Y33" s="30"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="29"/>
+      <c r="AB33" s="30"/>
+      <c r="AC33" s="31"/>
+      <c r="AD33" s="29"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="29"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="31"/>
+      <c r="AJ33" s="29"/>
+      <c r="AK33" s="30"/>
+      <c r="AL33" s="31"/>
+      <c r="AM33" s="29"/>
+      <c r="AN33" s="30"/>
+      <c r="AO33" s="31"/>
+      <c r="AP33" s="29"/>
+      <c r="AQ33" s="30"/>
+      <c r="AR33" s="31"/>
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B34" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="40"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="39"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="39"/>
-      <c r="V34" s="40"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="39"/>
-      <c r="Y34" s="40"/>
-      <c r="Z34" s="41"/>
-      <c r="AA34" s="39"/>
-      <c r="AB34" s="40"/>
-      <c r="AC34" s="41"/>
-      <c r="AD34" s="39"/>
-      <c r="AE34" s="40"/>
-      <c r="AF34" s="41"/>
-      <c r="AG34" s="39"/>
-      <c r="AH34" s="40"/>
-      <c r="AI34" s="41"/>
-      <c r="AJ34" s="39"/>
-      <c r="AK34" s="40"/>
-      <c r="AL34" s="41"/>
-      <c r="AM34" s="39"/>
-      <c r="AN34" s="40"/>
-      <c r="AO34" s="41"/>
-      <c r="AP34" s="39"/>
-      <c r="AQ34" s="40"/>
-      <c r="AR34" s="41"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="29"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="29"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="29"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="29"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="29"/>
+      <c r="AK34" s="30"/>
+      <c r="AL34" s="31"/>
+      <c r="AM34" s="29"/>
+      <c r="AN34" s="30"/>
+      <c r="AO34" s="31"/>
+      <c r="AP34" s="29"/>
+      <c r="AQ34" s="30"/>
+      <c r="AR34" s="31"/>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B35" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="39"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="39"/>
-      <c r="V35" s="40"/>
-      <c r="W35" s="41"/>
-      <c r="X35" s="39"/>
-      <c r="Y35" s="40"/>
-      <c r="Z35" s="41"/>
-      <c r="AA35" s="39"/>
-      <c r="AB35" s="40"/>
-      <c r="AC35" s="41"/>
-      <c r="AD35" s="39"/>
-      <c r="AE35" s="40"/>
-      <c r="AF35" s="41"/>
-      <c r="AG35" s="39"/>
-      <c r="AH35" s="40"/>
-      <c r="AI35" s="41"/>
-      <c r="AJ35" s="39"/>
-      <c r="AK35" s="40"/>
-      <c r="AL35" s="41"/>
-      <c r="AM35" s="39"/>
-      <c r="AN35" s="40"/>
-      <c r="AO35" s="41"/>
-      <c r="AP35" s="39"/>
-      <c r="AQ35" s="40"/>
-      <c r="AR35" s="41"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="29"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="29"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="31"/>
+      <c r="AD35" s="29"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="29"/>
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="31"/>
+      <c r="AJ35" s="29"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="31"/>
+      <c r="AM35" s="29"/>
+      <c r="AN35" s="30"/>
+      <c r="AO35" s="31"/>
+      <c r="AP35" s="29"/>
+      <c r="AQ35" s="30"/>
+      <c r="AR35" s="31"/>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B36" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="39"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="39"/>
-      <c r="V36" s="40"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="39"/>
-      <c r="Y36" s="40"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="39"/>
-      <c r="AB36" s="40"/>
-      <c r="AC36" s="41"/>
-      <c r="AD36" s="39"/>
-      <c r="AE36" s="40"/>
-      <c r="AF36" s="41"/>
-      <c r="AG36" s="39"/>
-      <c r="AH36" s="40"/>
-      <c r="AI36" s="41"/>
-      <c r="AJ36" s="39"/>
-      <c r="AK36" s="40"/>
-      <c r="AL36" s="41"/>
-      <c r="AM36" s="39"/>
-      <c r="AN36" s="40"/>
-      <c r="AO36" s="41"/>
-      <c r="AP36" s="39"/>
-      <c r="AQ36" s="40"/>
-      <c r="AR36" s="41"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="31"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="29"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="31"/>
+      <c r="AA36" s="29"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="31"/>
+      <c r="AD36" s="29"/>
+      <c r="AE36" s="30"/>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="29"/>
+      <c r="AH36" s="30"/>
+      <c r="AI36" s="31"/>
+      <c r="AJ36" s="29"/>
+      <c r="AK36" s="30"/>
+      <c r="AL36" s="31"/>
+      <c r="AM36" s="29"/>
+      <c r="AN36" s="30"/>
+      <c r="AO36" s="31"/>
+      <c r="AP36" s="29"/>
+      <c r="AQ36" s="30"/>
+      <c r="AR36" s="31"/>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B37" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="41"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="39"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="39"/>
-      <c r="V37" s="40"/>
-      <c r="W37" s="41"/>
-      <c r="X37" s="39"/>
-      <c r="Y37" s="40"/>
-      <c r="Z37" s="41"/>
-      <c r="AA37" s="39"/>
-      <c r="AB37" s="40"/>
-      <c r="AC37" s="41"/>
-      <c r="AD37" s="39"/>
-      <c r="AE37" s="40"/>
-      <c r="AF37" s="41"/>
-      <c r="AG37" s="39"/>
-      <c r="AH37" s="40"/>
-      <c r="AI37" s="41"/>
-      <c r="AJ37" s="39"/>
-      <c r="AK37" s="40"/>
-      <c r="AL37" s="41"/>
-      <c r="AM37" s="39"/>
-      <c r="AN37" s="40"/>
-      <c r="AO37" s="41"/>
-      <c r="AP37" s="39"/>
-      <c r="AQ37" s="40"/>
-      <c r="AR37" s="41"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="29"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="29"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="29"/>
+      <c r="AH37" s="30"/>
+      <c r="AI37" s="31"/>
+      <c r="AJ37" s="29"/>
+      <c r="AK37" s="30"/>
+      <c r="AL37" s="31"/>
+      <c r="AM37" s="29"/>
+      <c r="AN37" s="30"/>
+      <c r="AO37" s="31"/>
+      <c r="AP37" s="29"/>
+      <c r="AQ37" s="30"/>
+      <c r="AR37" s="31"/>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B38" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="39"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="39"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="39"/>
-      <c r="V38" s="40"/>
-      <c r="W38" s="41"/>
-      <c r="X38" s="39"/>
-      <c r="Y38" s="40"/>
-      <c r="Z38" s="41"/>
-      <c r="AA38" s="39"/>
-      <c r="AB38" s="40"/>
-      <c r="AC38" s="41"/>
-      <c r="AD38" s="39"/>
-      <c r="AE38" s="40"/>
-      <c r="AF38" s="41"/>
-      <c r="AG38" s="39"/>
-      <c r="AH38" s="40"/>
-      <c r="AI38" s="41"/>
-      <c r="AJ38" s="39"/>
-      <c r="AK38" s="40"/>
-      <c r="AL38" s="41"/>
-      <c r="AM38" s="39"/>
-      <c r="AN38" s="40"/>
-      <c r="AO38" s="41"/>
-      <c r="AP38" s="39"/>
-      <c r="AQ38" s="40"/>
-      <c r="AR38" s="41"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="31"/>
+      <c r="X38" s="29"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="31"/>
+      <c r="AA38" s="29"/>
+      <c r="AB38" s="30"/>
+      <c r="AC38" s="31"/>
+      <c r="AD38" s="29"/>
+      <c r="AE38" s="30"/>
+      <c r="AF38" s="31"/>
+      <c r="AG38" s="29"/>
+      <c r="AH38" s="30"/>
+      <c r="AI38" s="31"/>
+      <c r="AJ38" s="29"/>
+      <c r="AK38" s="30"/>
+      <c r="AL38" s="31"/>
+      <c r="AM38" s="29"/>
+      <c r="AN38" s="30"/>
+      <c r="AO38" s="31"/>
+      <c r="AP38" s="29"/>
+      <c r="AQ38" s="30"/>
+      <c r="AR38" s="31"/>
     </row>
     <row r="39" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B39" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="39"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="39"/>
-      <c r="V39" s="40"/>
-      <c r="W39" s="41"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="40"/>
-      <c r="Z39" s="41"/>
-      <c r="AA39" s="39"/>
-      <c r="AB39" s="40"/>
-      <c r="AC39" s="41"/>
-      <c r="AD39" s="39"/>
-      <c r="AE39" s="40"/>
-      <c r="AF39" s="41"/>
-      <c r="AG39" s="39"/>
-      <c r="AH39" s="40"/>
-      <c r="AI39" s="41"/>
-      <c r="AJ39" s="39"/>
-      <c r="AK39" s="40"/>
-      <c r="AL39" s="41"/>
-      <c r="AM39" s="39"/>
-      <c r="AN39" s="40"/>
-      <c r="AO39" s="41"/>
-      <c r="AP39" s="39"/>
-      <c r="AQ39" s="40"/>
-      <c r="AR39" s="41"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="31"/>
+      <c r="X39" s="29"/>
+      <c r="Y39" s="30"/>
+      <c r="Z39" s="31"/>
+      <c r="AA39" s="29"/>
+      <c r="AB39" s="30"/>
+      <c r="AC39" s="31"/>
+      <c r="AD39" s="29"/>
+      <c r="AE39" s="30"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="29"/>
+      <c r="AH39" s="30"/>
+      <c r="AI39" s="31"/>
+      <c r="AJ39" s="29"/>
+      <c r="AK39" s="30"/>
+      <c r="AL39" s="31"/>
+      <c r="AM39" s="29"/>
+      <c r="AN39" s="30"/>
+      <c r="AO39" s="31"/>
+      <c r="AP39" s="29"/>
+      <c r="AQ39" s="30"/>
+      <c r="AR39" s="31"/>
     </row>
     <row r="40" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B40" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="41"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="39"/>
-      <c r="S40" s="40"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="39"/>
-      <c r="V40" s="40"/>
-      <c r="W40" s="41"/>
-      <c r="X40" s="39"/>
-      <c r="Y40" s="40"/>
-      <c r="Z40" s="41"/>
-      <c r="AA40" s="39"/>
-      <c r="AB40" s="40"/>
-      <c r="AC40" s="41"/>
-      <c r="AD40" s="39"/>
-      <c r="AE40" s="40"/>
-      <c r="AF40" s="41"/>
-      <c r="AG40" s="39"/>
-      <c r="AH40" s="40"/>
-      <c r="AI40" s="41"/>
-      <c r="AJ40" s="39"/>
-      <c r="AK40" s="40"/>
-      <c r="AL40" s="41"/>
-      <c r="AM40" s="39"/>
-      <c r="AN40" s="40"/>
-      <c r="AO40" s="41"/>
-      <c r="AP40" s="39"/>
-      <c r="AQ40" s="40"/>
-      <c r="AR40" s="41"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="29"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="29"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="29"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="31"/>
+      <c r="AG40" s="29"/>
+      <c r="AH40" s="30"/>
+      <c r="AI40" s="31"/>
+      <c r="AJ40" s="29"/>
+      <c r="AK40" s="30"/>
+      <c r="AL40" s="31"/>
+      <c r="AM40" s="29"/>
+      <c r="AN40" s="30"/>
+      <c r="AO40" s="31"/>
+      <c r="AP40" s="29"/>
+      <c r="AQ40" s="30"/>
+      <c r="AR40" s="31"/>
     </row>
     <row r="41" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B41" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="41"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="39"/>
-      <c r="S41" s="40"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="39"/>
-      <c r="V41" s="40"/>
-      <c r="W41" s="41"/>
-      <c r="X41" s="39"/>
-      <c r="Y41" s="40"/>
-      <c r="Z41" s="41"/>
-      <c r="AA41" s="39"/>
-      <c r="AB41" s="40"/>
-      <c r="AC41" s="41"/>
-      <c r="AD41" s="39"/>
-      <c r="AE41" s="40"/>
-      <c r="AF41" s="41"/>
-      <c r="AG41" s="39"/>
-      <c r="AH41" s="40"/>
-      <c r="AI41" s="41"/>
-      <c r="AJ41" s="39"/>
-      <c r="AK41" s="40"/>
-      <c r="AL41" s="41"/>
-      <c r="AM41" s="39"/>
-      <c r="AN41" s="40"/>
-      <c r="AO41" s="41"/>
-      <c r="AP41" s="39"/>
-      <c r="AQ41" s="40"/>
-      <c r="AR41" s="41"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="30"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="30"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="29"/>
+      <c r="Y41" s="30"/>
+      <c r="Z41" s="31"/>
+      <c r="AA41" s="29"/>
+      <c r="AB41" s="30"/>
+      <c r="AC41" s="31"/>
+      <c r="AD41" s="29"/>
+      <c r="AE41" s="30"/>
+      <c r="AF41" s="31"/>
+      <c r="AG41" s="29"/>
+      <c r="AH41" s="30"/>
+      <c r="AI41" s="31"/>
+      <c r="AJ41" s="29"/>
+      <c r="AK41" s="30"/>
+      <c r="AL41" s="31"/>
+      <c r="AM41" s="29"/>
+      <c r="AN41" s="30"/>
+      <c r="AO41" s="31"/>
+      <c r="AP41" s="29"/>
+      <c r="AQ41" s="30"/>
+      <c r="AR41" s="31"/>
     </row>
     <row r="42" spans="1:44" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B42" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="39"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="40"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="39"/>
-      <c r="M42" s="40"/>
-      <c r="N42" s="41"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="39"/>
-      <c r="S42" s="40"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="39"/>
-      <c r="V42" s="40"/>
-      <c r="W42" s="41"/>
-      <c r="X42" s="39"/>
-      <c r="Y42" s="40"/>
-      <c r="Z42" s="41"/>
-      <c r="AA42" s="39"/>
-      <c r="AB42" s="40"/>
-      <c r="AC42" s="41"/>
-      <c r="AD42" s="39"/>
-      <c r="AE42" s="40"/>
-      <c r="AF42" s="41"/>
-      <c r="AG42" s="39"/>
-      <c r="AH42" s="40"/>
-      <c r="AI42" s="41"/>
-      <c r="AJ42" s="39"/>
-      <c r="AK42" s="40"/>
-      <c r="AL42" s="41"/>
-      <c r="AM42" s="39"/>
-      <c r="AN42" s="40"/>
-      <c r="AO42" s="41"/>
-      <c r="AP42" s="39"/>
-      <c r="AQ42" s="40"/>
-      <c r="AR42" s="41"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="29"/>
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="29"/>
+      <c r="AB42" s="30"/>
+      <c r="AC42" s="31"/>
+      <c r="AD42" s="29"/>
+      <c r="AE42" s="30"/>
+      <c r="AF42" s="31"/>
+      <c r="AG42" s="29"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="31"/>
+      <c r="AJ42" s="29"/>
+      <c r="AK42" s="30"/>
+      <c r="AL42" s="31"/>
+      <c r="AM42" s="29"/>
+      <c r="AN42" s="30"/>
+      <c r="AO42" s="31"/>
+      <c r="AP42" s="29"/>
+      <c r="AQ42" s="30"/>
+      <c r="AR42" s="31"/>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B43" s="42"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="43"/>
-      <c r="M43" s="44"/>
-      <c r="N43" s="45"/>
-      <c r="O43" s="43"/>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="45"/>
-      <c r="R43" s="43"/>
-      <c r="S43" s="44"/>
-      <c r="T43" s="45"/>
-      <c r="U43" s="43"/>
-      <c r="V43" s="44"/>
-      <c r="W43" s="45"/>
-      <c r="X43" s="43"/>
-      <c r="Y43" s="44"/>
-      <c r="Z43" s="45"/>
-      <c r="AA43" s="43"/>
-      <c r="AB43" s="44"/>
-      <c r="AC43" s="45"/>
-      <c r="AD43" s="43"/>
-      <c r="AE43" s="44"/>
-      <c r="AF43" s="45"/>
-      <c r="AG43" s="43"/>
-      <c r="AH43" s="44"/>
-      <c r="AI43" s="45"/>
-      <c r="AJ43" s="43"/>
-      <c r="AK43" s="44"/>
-      <c r="AL43" s="45"/>
-      <c r="AM43" s="43"/>
-      <c r="AN43" s="44"/>
-      <c r="AO43" s="45"/>
-      <c r="AP43" s="43"/>
-      <c r="AQ43" s="44"/>
-      <c r="AR43" s="45"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="35"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="34"/>
+      <c r="T43" s="35"/>
+      <c r="U43" s="33"/>
+      <c r="V43" s="34"/>
+      <c r="W43" s="35"/>
+      <c r="X43" s="33"/>
+      <c r="Y43" s="34"/>
+      <c r="Z43" s="35"/>
+      <c r="AA43" s="33"/>
+      <c r="AB43" s="34"/>
+      <c r="AC43" s="35"/>
+      <c r="AD43" s="33"/>
+      <c r="AE43" s="34"/>
+      <c r="AF43" s="35"/>
+      <c r="AG43" s="33"/>
+      <c r="AH43" s="34"/>
+      <c r="AI43" s="35"/>
+      <c r="AJ43" s="33"/>
+      <c r="AK43" s="34"/>
+      <c r="AL43" s="35"/>
+      <c r="AM43" s="33"/>
+      <c r="AN43" s="34"/>
+      <c r="AO43" s="35"/>
+      <c r="AP43" s="33"/>
+      <c r="AQ43" s="34"/>
+      <c r="AR43" s="35"/>
     </row>
     <row r="44" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A44" s="1"/>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="43">
         <f>AVERAGE(C4:C43)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="47"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="47">
+      <c r="D44" s="43"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="43">
         <f>AVERAGE(F4:F43)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="47">
+      <c r="G44" s="43"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="43">
         <f>AVERAGE(I4:I43)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="47"/>
-      <c r="K44" s="48"/>
-      <c r="L44" s="47">
+      <c r="J44" s="43"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="43">
         <f>AVERAGE(L4:L43)</f>
         <v>0</v>
       </c>
-      <c r="M44" s="47"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="47">
+      <c r="M44" s="43"/>
+      <c r="N44" s="44"/>
+      <c r="O44" s="43">
         <f>AVERAGE(O4:O43)</f>
         <v>0</v>
       </c>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="48"/>
-      <c r="R44" s="47">
+      <c r="P44" s="43"/>
+      <c r="Q44" s="44"/>
+      <c r="R44" s="43">
         <f>AVERAGE(R4:R43)</f>
         <v>0</v>
       </c>
-      <c r="S44" s="47"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="47">
+      <c r="S44" s="43"/>
+      <c r="T44" s="44"/>
+      <c r="U44" s="43">
         <f>AVERAGE(U4:U43)</f>
         <v>0</v>
       </c>
-      <c r="V44" s="47"/>
-      <c r="W44" s="48"/>
-      <c r="X44" s="47">
+      <c r="V44" s="43"/>
+      <c r="W44" s="44"/>
+      <c r="X44" s="43">
         <f>AVERAGE(X4:X43)</f>
         <v>0</v>
       </c>
-      <c r="Y44" s="47"/>
-      <c r="Z44" s="48"/>
-      <c r="AA44" s="47">
+      <c r="Y44" s="43"/>
+      <c r="Z44" s="44"/>
+      <c r="AA44" s="43">
         <f>AVERAGE(AA4:AA43)</f>
         <v>0</v>
       </c>
-      <c r="AB44" s="47"/>
-      <c r="AC44" s="48"/>
-      <c r="AD44" s="47">
+      <c r="AB44" s="43"/>
+      <c r="AC44" s="44"/>
+      <c r="AD44" s="43">
         <f>AVERAGE(AD4:AD43)</f>
         <v>0</v>
       </c>
-      <c r="AE44" s="47"/>
-      <c r="AF44" s="48"/>
-      <c r="AG44" s="47">
+      <c r="AE44" s="43"/>
+      <c r="AF44" s="44"/>
+      <c r="AG44" s="43">
         <f>AVERAGE(AG4:AG43)</f>
         <v>0</v>
       </c>
-      <c r="AH44" s="47"/>
-      <c r="AI44" s="48"/>
-      <c r="AJ44" s="47">
+      <c r="AH44" s="43"/>
+      <c r="AI44" s="44"/>
+      <c r="AJ44" s="43">
         <f>AVERAGE(AJ4:AJ43)</f>
         <v>0</v>
       </c>
-      <c r="AK44" s="47"/>
-      <c r="AL44" s="48"/>
-      <c r="AM44" s="47">
+      <c r="AK44" s="43"/>
+      <c r="AL44" s="44"/>
+      <c r="AM44" s="43">
         <f>AVERAGE(AM4:AM43)</f>
         <v>0</v>
       </c>
-      <c r="AN44" s="47"/>
-      <c r="AO44" s="48"/>
-      <c r="AP44" s="47">
+      <c r="AN44" s="43"/>
+      <c r="AO44" s="44"/>
+      <c r="AP44" s="43">
         <f>AVERAGE(AP4:AP43)</f>
         <v>0</v>
       </c>
-      <c r="AQ44" s="47"/>
-      <c r="AR44" s="48"/>
+      <c r="AQ44" s="43"/>
+      <c r="AR44" s="44"/>
     </row>
     <row r="45" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B45" s="15"/>

--- a/activity/M01A11/M01A11_BordeLibre.xlsx
+++ b/activity/M01A11/M01A11_BordeLibre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29317"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13966316-405F-4CAA-AA64-59C76D824E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1040DD21-1215-4610-B316-BF83C48D2F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -660,6 +660,18 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -668,18 +680,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2501,96 +2501,96 @@
     </row>
     <row r="2" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="40" t="str">
+      <c r="C2" s="44" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="40" t="str">
+      <c r="D2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="44" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="40" t="str">
+      <c r="G2" s="45"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="44" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="41"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="40" t="str">
+      <c r="J2" s="45"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="44" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="41"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="40" t="str">
+      <c r="M2" s="45"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="44" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="40" t="str">
+      <c r="P2" s="45"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="44" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="41"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="40" t="str">
+      <c r="S2" s="45"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="44" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="41"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="40" t="str">
+      <c r="V2" s="45"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="44" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="40" t="str">
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="44" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="40" t="str">
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="44" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="40" t="str">
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="46"/>
+      <c r="AG2" s="44" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="40" t="str">
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="44" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="42"/>
-      <c r="AM2" s="40" t="str">
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="46"/>
+      <c r="AM2" s="44" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="41"/>
-      <c r="AO2" s="42"/>
-      <c r="AP2" s="40" t="str">
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="46"/>
+      <c r="AP2" s="44" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="41"/>
-      <c r="AR2" s="42"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="46"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="46"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -4629,90 +4629,90 @@
       <c r="B44" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="43">
+      <c r="C44" s="42">
         <f>AVERAGE(C4:C43)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="43">
+      <c r="D44" s="42"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="42">
         <f>AVERAGE(F4:F43)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="43"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="43">
+      <c r="G44" s="42"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="42">
         <f>AVERAGE(I4:I43)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="43"/>
-      <c r="K44" s="44"/>
-      <c r="L44" s="43">
+      <c r="J44" s="42"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="42">
         <f>AVERAGE(L4:L43)</f>
         <v>0</v>
       </c>
-      <c r="M44" s="43"/>
-      <c r="N44" s="44"/>
-      <c r="O44" s="43">
+      <c r="M44" s="42"/>
+      <c r="N44" s="43"/>
+      <c r="O44" s="42">
         <f>AVERAGE(O4:O43)</f>
         <v>0</v>
       </c>
-      <c r="P44" s="43"/>
-      <c r="Q44" s="44"/>
-      <c r="R44" s="43">
+      <c r="P44" s="42"/>
+      <c r="Q44" s="43"/>
+      <c r="R44" s="42">
         <f>AVERAGE(R4:R43)</f>
         <v>0</v>
       </c>
-      <c r="S44" s="43"/>
-      <c r="T44" s="44"/>
-      <c r="U44" s="43">
+      <c r="S44" s="42"/>
+      <c r="T44" s="43"/>
+      <c r="U44" s="42">
         <f>AVERAGE(U4:U43)</f>
         <v>0</v>
       </c>
-      <c r="V44" s="43"/>
-      <c r="W44" s="44"/>
-      <c r="X44" s="43">
+      <c r="V44" s="42"/>
+      <c r="W44" s="43"/>
+      <c r="X44" s="42">
         <f>AVERAGE(X4:X43)</f>
         <v>0</v>
       </c>
-      <c r="Y44" s="43"/>
-      <c r="Z44" s="44"/>
-      <c r="AA44" s="43">
+      <c r="Y44" s="42"/>
+      <c r="Z44" s="43"/>
+      <c r="AA44" s="42">
         <f>AVERAGE(AA4:AA43)</f>
         <v>0</v>
       </c>
-      <c r="AB44" s="43"/>
-      <c r="AC44" s="44"/>
-      <c r="AD44" s="43">
+      <c r="AB44" s="42"/>
+      <c r="AC44" s="43"/>
+      <c r="AD44" s="42">
         <f>AVERAGE(AD4:AD43)</f>
         <v>0</v>
       </c>
-      <c r="AE44" s="43"/>
-      <c r="AF44" s="44"/>
-      <c r="AG44" s="43">
+      <c r="AE44" s="42"/>
+      <c r="AF44" s="43"/>
+      <c r="AG44" s="42">
         <f>AVERAGE(AG4:AG43)</f>
         <v>0</v>
       </c>
-      <c r="AH44" s="43"/>
-      <c r="AI44" s="44"/>
-      <c r="AJ44" s="43">
+      <c r="AH44" s="42"/>
+      <c r="AI44" s="43"/>
+      <c r="AJ44" s="42">
         <f>AVERAGE(AJ4:AJ43)</f>
         <v>0</v>
       </c>
-      <c r="AK44" s="43"/>
-      <c r="AL44" s="44"/>
-      <c r="AM44" s="43">
+      <c r="AK44" s="42"/>
+      <c r="AL44" s="43"/>
+      <c r="AM44" s="42">
         <f>AVERAGE(AM4:AM43)</f>
         <v>0</v>
       </c>
-      <c r="AN44" s="43"/>
-      <c r="AO44" s="44"/>
-      <c r="AP44" s="43">
+      <c r="AN44" s="42"/>
+      <c r="AO44" s="43"/>
+      <c r="AP44" s="42">
         <f>AVERAGE(AP4:AP43)</f>
         <v>0</v>
       </c>
-      <c r="AQ44" s="43"/>
-      <c r="AR44" s="44"/>
+      <c r="AQ44" s="42"/>
+      <c r="AR44" s="43"/>
     </row>
     <row r="45" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B45" s="15"/>
@@ -6336,19 +6336,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U44:W44"/>
-    <mergeCell ref="AM44:AO44"/>
-    <mergeCell ref="X44:Z44"/>
-    <mergeCell ref="AA44:AC44"/>
-    <mergeCell ref="AD44:AF44"/>
-    <mergeCell ref="AG44:AI44"/>
-    <mergeCell ref="AJ44:AL44"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="L44:N44"/>
-    <mergeCell ref="O44:Q44"/>
-    <mergeCell ref="R44:T44"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="C2:E2"/>
@@ -6365,6 +6352,19 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U44:W44"/>
+    <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="X44:Z44"/>
+    <mergeCell ref="AA44:AC44"/>
+    <mergeCell ref="AD44:AF44"/>
+    <mergeCell ref="AG44:AI44"/>
+    <mergeCell ref="AJ44:AL44"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="O44:Q44"/>
+    <mergeCell ref="R44:T44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
